--- a/4 четверть_9_JavaScript_Escape.xlsx
+++ b/4 четверть_9_JavaScript_Escape.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAD22056-56C1-42F7-ADB3-AB31F133284A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{290E872E-70CE-40EC-AD4C-E890CFBB1399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -317,12 +317,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -427,11 +435,11 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -442,32 +450,35 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -857,7 +868,7 @@
       <c r="B9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="14" t="s">
         <v>12</v>
       </c>
     </row>

--- a/4 четверть_9_JavaScript_Escape.xlsx
+++ b/4 четверть_9_JavaScript_Escape.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{290E872E-70CE-40EC-AD4C-E890CFBB1399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B39A201-4D74-44D4-956E-37B2CE07CA5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24" yWindow="1104" windowWidth="23016" windowHeight="11136" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="import require" sheetId="17" r:id="rId1"/>
@@ -33,46 +33,6 @@
     <t>Безопасный доступ и присвоение</t>
   </si>
   <si>
-    <t>?? (Nullish Coalescing) — Оператор нулевого слияния</t>
-  </si>
-  <si>
-    <t>?. (Optional Chaining) — Безопасный доступ к свойствам</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Срабатывает: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>null, undefined, 0, '', false</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Срабатывает: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>null, undefined</t>
-    </r>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">const userInput = 0;
 const valueWithOr = </t>
@@ -129,108 +89,97 @@
     </r>
   </si>
   <si>
-    <t>Безопасный доступ к свойству, которого нет</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">безопасный </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>вызов</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> или </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>доступ к внутренним свойствам</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">присваивание </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>новой</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> переменной</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">присваивание </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>текущей</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> переменной</t>
-    </r>
-  </si>
-  <si>
-    <t>Безопасный вызов метода.</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>isLoggedIn &amp;&amp; logout();</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>if (isLoggedIn) logout(); // то же самое, что</t>
+    </r>
   </si>
   <si>
     <r>
       <t>const user = { profile: { name: "Алекс" } };
-const result = user?.profile?.getFullName?.(); //
+const city =</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> user?.profile?.address?.city; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">// Выведет: undefined </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">const user = { profile: { name: "Алекс" } };
+const result = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>user?.profile?.getFullName?.();</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> //
 1</t>
     </r>
     <r>
@@ -271,53 +220,452 @@
     </r>
   </si>
   <si>
-    <t>Логические операторы присваивания: ||= и &amp;&amp;=</t>
-  </si>
-  <si>
-    <r>
-      <t>const user = { profile: { name: "Алекс" } };
-const city = user?.profile?.address?.city;</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> // Выведет: undefined </t>
-    </r>
-  </si>
-  <si>
-    <t>let a = false;
-a ||= true; // a станет true, так как false — ложное значение</t>
-  </si>
-  <si>
-    <t>let b = 10;
-b &amp;&amp;= 20;   // b станет 20, так как 10 — истинное значение</t>
-  </si>
-  <si>
-    <t>let c = null;
-c ??= 5;    // c станет 5, так как null — это nullish</t>
-  </si>
-  <si>
-    <t>если истинное, то поменять</t>
-  </si>
-  <si>
-    <t>если ложное, то поменять</t>
-  </si>
-  <si>
-    <t>если null, то поменять</t>
+    <r>
+      <t xml:space="preserve">let a = false;
+a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>||=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> true; //</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Аналог! a =  a || true</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+// a станет true, так как false — ложное значение</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">let b = 10;
+b </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">&amp;&amp;= </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>20;   //</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Аналог! b = b &amp;&amp; 20; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+// b станет 20, так как 10 — истинное значение</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">let c = null;
+c </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">??= </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">5;  // </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Аналог! c =  c ?? 5;    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+// c станет 5, так как null — это nullish</t>
+    </r>
+  </si>
+  <si>
+    <t>||</t>
+  </si>
+  <si>
+    <t>??</t>
+  </si>
+  <si>
+    <t>&amp;&amp;</t>
+  </si>
+  <si>
+    <t>НОВОЙ</t>
+  </si>
+  <si>
+    <t>ТОЙ ЖЕ</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Вернуть/вызвать </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Default</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> если </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>null, undefined, 0, '', false</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Вернуть/вызвать</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Default</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> если </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>null, undefined</t>
+    </r>
+  </si>
+  <si>
+    <t>Безопасный возврат/вызов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вернуть/вызвать Default </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Безопасный доступ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> к свойству, которого нет
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Как работает</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>user?.profile</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>если user есть</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, возвращаем profile</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Безопасный вызов</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> метода.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Безопасный возврат/вызов
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Как работает</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1 Вычисляется левый операнд.
+2 Если он falsy — правый не вычисляется, возвращается левое значение как есть.
+3 Если он truthy — вычисляется правый операнд и возвращается он.</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -391,6 +739,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -439,7 +795,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -469,17 +825,20 @@
     <xf numFmtId="49" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -767,12 +1126,12 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:V13"/>
+  <dimension ref="A2:V12"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="62.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="81.109375" style="4" customWidth="1"/>
+    <col min="2" max="2" width="49.88671875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="56.6640625" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="56.44140625" style="1" customWidth="1"/>
     <col min="5" max="5" width="6.33203125" style="3" customWidth="1"/>
     <col min="6" max="6" width="43.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -818,92 +1177,89 @@
       <c r="U3" s="1"/>
       <c r="V3" s="2"/>
     </row>
-    <row r="4" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="9"/>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A4" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="12"/>
+      <c r="C4" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>13</v>
+      </c>
       <c r="P4" s="1"/>
       <c r="U4" s="1"/>
       <c r="V4" s="2"/>
     </row>
-    <row r="5" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B5" s="1" t="s">
-        <v>3</v>
+    <row r="5" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>14</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>5</v>
+        <v>1</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B6" s="1" t="s">
-        <v>4</v>
+    <row r="6" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>15</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>8</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="B7" s="12"/>
       <c r="C7" s="1"/>
     </row>
-    <row r="8" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B8" s="2" t="s">
+    <row r="8" spans="1:22" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="11" t="s">
-        <v>14</v>
-      </c>
     </row>
-    <row r="9" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="B9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>12</v>
+    <row r="9" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B9" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="11"/>
+    <row r="10" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="B10" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B11" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B12" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B13" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>17</v>
-      </c>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
